--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:27:05</t>
+          <t>Última actualización: 05:50:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -587,6 +587,32 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>05:49:35</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>92</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -612,7 +638,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:27:05</t>
+          <t>Última actualización: 05:50:26</t>
         </is>
       </c>
     </row>
@@ -647,7 +673,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:27:05</t>
+          <t>Última actualización: 05:50:26</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:50:26</t>
+          <t>Última actualización: 06:21:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 5</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -613,6 +613,110 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>06:20:31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06:33</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06:20:31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07:19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06:20:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>06:20:31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -638,7 +742,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:50:26</t>
+          <t>Última actualización: 06:21:17</t>
         </is>
       </c>
     </row>
@@ -660,7 +764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,16 +777,74 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:50:26</t>
+          <t>Última actualización: 06:21:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
-        </is>
-      </c>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06:21:16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:21:17</t>
+          <t>Última actualización: 06:43:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -717,6 +717,110 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>06:42:35</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>73</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>06:42:35</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>78</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>06:42:35</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>79</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>06:42:35</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>89</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -742,7 +846,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:21:17</t>
+          <t>Última actualización: 06:43:20</t>
         </is>
       </c>
     </row>
@@ -777,7 +881,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:21:17</t>
+          <t>Última actualización: 06:43:20</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:43:20</t>
+          <t>Última actualización: 06:53:37</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -821,6 +821,58 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>06:52:51</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>44</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>06:52:51</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>97</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -846,7 +898,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:43:20</t>
+          <t>Última actualización: 06:53:37</t>
         </is>
       </c>
     </row>
@@ -881,7 +933,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:43:20</t>
+          <t>Última actualización: 06:53:37</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:53:37</t>
+          <t>Última actualización: 07:21:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 19</t>
         </is>
       </c>
     </row>
@@ -873,6 +873,110 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>07:20:39</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>17</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>07:20:39</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>53</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>07:20:39</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>81</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>07:20:39</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>91</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -898,7 +1002,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:53:37</t>
+          <t>Última actualización: 07:21:20</t>
         </is>
       </c>
     </row>
@@ -920,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -933,14 +1037,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:53:37</t>
+          <t>Última actualización: 07:21:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1105,58 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>07:21:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>90</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07:21:20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:21:20</t>
+          <t>Última actualización: 07:46:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 19</t>
+          <t>Total filas: 25</t>
         </is>
       </c>
     </row>
@@ -977,6 +977,162 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>07:45:28</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>21</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>07:45:28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>44</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>07:45:28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>65</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>07:45:28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>81</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>07:45:28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>93</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>07:45:28</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>94</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1002,7 +1158,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:21:20</t>
+          <t>Última actualización: 07:46:09</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1193,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:21:20</t>
+          <t>Última actualización: 07:46:09</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:46:09</t>
+          <t>Última actualización: 07:56:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 25</t>
+          <t>Total filas: 27</t>
         </is>
       </c>
     </row>
@@ -1133,6 +1133,58 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>07:55:42</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>82</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>07:55:42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>94</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1158,7 +1210,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:46:09</t>
+          <t>Última actualización: 07:56:23</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,14 +1245,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:46:09</t>
+          <t>Última actualización: 07:56:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -1313,6 +1365,32 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07:56:23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>85</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:56:23</t>
+          <t>Última actualización: 08:17:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 27</t>
+          <t>Total filas: 33</t>
         </is>
       </c>
     </row>
@@ -1185,6 +1185,162 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>08:16:46</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>49</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>08:16:46</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>59</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>08:16:46</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>75</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>08:16:46</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>80</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>08:16:46</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>83</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>08:16:46</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>97</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1210,7 +1366,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:56:23</t>
+          <t>Última actualización: 08:17:27</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1401,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:56:23</t>
+          <t>Última actualización: 08:17:27</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:17:27</t>
+          <t>Última actualización: 08:39:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 33</t>
+          <t>Total filas: 43</t>
         </is>
       </c>
     </row>
@@ -1341,6 +1341,266 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>27</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>28</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>51</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>53</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>58</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>61</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>65</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>80</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1353,7 +1613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,16 +1626,74 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:17:27</t>
+          <t>Última actualización: 08:39:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
-        </is>
-      </c>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>08:39:08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1401,7 +1719,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:17:27</t>
+          <t>Última actualización: 08:39:49</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:39:49</t>
+          <t>Última actualización: 08:51:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 43</t>
+          <t>Total filas: 49</t>
         </is>
       </c>
     </row>
@@ -1601,6 +1601,162 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>08:50:29</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>08:50:29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>45</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>08:50:29</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>53</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>08:50:29</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>83</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>08:50:29</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>93</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>08:50:29</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>95</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1626,7 +1782,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:39:49</t>
+          <t>Última actualización: 08:51:09</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1875,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:39:49</t>
+          <t>Última actualización: 08:51:09</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:51:09</t>
+          <t>Última actualización: 09:40:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 49</t>
+          <t>Total filas: 62</t>
         </is>
       </c>
     </row>
@@ -1757,6 +1757,344 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>50</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>50</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>65</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>15_P INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>67</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>76</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>77</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>78</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>82</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>87</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>91</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>09:39:36</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>96</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1782,7 +2120,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:51:09</t>
+          <t>Última actualización: 09:40:17</t>
         </is>
       </c>
     </row>
@@ -1862,7 +2200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,14 +2213,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:51:09</t>
+          <t>Última actualización: 09:40:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -2021,6 +2359,84 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09:39:57</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>09:40:17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09:40:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:40:17</t>
+          <t>Última actualización: 10:20:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 62</t>
+          <t>Total filas: 73</t>
         </is>
       </c>
     </row>
@@ -2095,6 +2095,292 @@
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>37</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>40</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>43</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>55</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>70</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>71</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>71</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>86</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>92</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>99</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2107,7 +2393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2120,14 +2406,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:40:17</t>
+          <t>Última actualización: 10:20:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -2188,6 +2474,32 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10:19:58</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2200,7 +2512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2213,14 +2525,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:40:17</t>
+          <t>Última actualización: 10:20:39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -2437,6 +2749,32 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10:20:19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>66</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:20:39</t>
+          <t>Última actualización: 10:48:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 73</t>
+          <t>Total filas: 80</t>
         </is>
       </c>
     </row>
@@ -2381,6 +2381,188 @@
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>38</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>44</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>68</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>78</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>90</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>95</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2393,7 +2575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2406,14 +2588,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:20:39</t>
+          <t>Última actualización: 10:48:30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -2500,6 +2682,58 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>44</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10:47:44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>95</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2525,7 +2759,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:20:39</t>
+          <t>Última actualización: 10:48:30</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:48:30</t>
+          <t>Última actualización: 11:19:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 80</t>
+          <t>Total filas: 87</t>
         </is>
       </c>
     </row>
@@ -2563,6 +2563,188 @@
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>48</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>75</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>76</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>77</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>77</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>90</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>11:18:53</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>90</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2588,7 +2770,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:48:30</t>
+          <t>Última actualización: 11:19:38</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2941,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:48:30</t>
+          <t>Última actualización: 11:19:38</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:19:38</t>
+          <t>Última actualización: 11:43:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 87</t>
+          <t>Total filas: 96</t>
         </is>
       </c>
     </row>
@@ -2745,6 +2745,240 @@
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>50</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>54</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>66</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>80</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>81</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>91</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>95</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2757,7 +2991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2770,14 +3004,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:19:38</t>
+          <t>Última actualización: 11:43:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -2916,6 +3150,32 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>11:43:15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>81</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2928,7 +3188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,14 +3201,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:19:38</t>
+          <t>Última actualización: 11:43:56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -3191,6 +3451,58 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11:43:36</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>89</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11:43:56</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>98</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:43:56</t>
+          <t>Última actualización: 11:54:33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 96</t>
+          <t>Total filas: 101</t>
         </is>
       </c>
     </row>
@@ -2979,6 +2979,136 @@
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>11:53:53</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>43</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>11:53:53</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>80</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>11:53:53</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>84</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>11:53:53</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>89</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>11:53:53</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>92</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3004,7 +3134,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:43:56</t>
+          <t>Última actualización: 11:54:33</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3331,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:43:56</t>
+          <t>Última actualización: 11:54:33</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:54:33</t>
+          <t>Última actualización: 12:20:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 101</t>
+          <t>Total filas: 106</t>
         </is>
       </c>
     </row>
@@ -3109,6 +3109,136 @@
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>12:19:19</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>18</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>12:19:19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>67</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>12:19:19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>74</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>12:19:19</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>74</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>12:19:19</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>95</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3121,7 +3251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3134,14 +3264,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:54:33</t>
+          <t>Última actualización: 12:20:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 5</t>
+          <t>Total filas: 6</t>
         </is>
       </c>
     </row>
@@ -3306,6 +3436,32 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12:19:19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>74</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3318,7 +3474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3331,14 +3487,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:54:33</t>
+          <t>Última actualización: 12:20:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -3633,6 +3789,32 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12:19:40</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>98</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:20:00</t>
+          <t>Última actualización: 12:42:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 106</t>
+          <t>Total filas: 108</t>
         </is>
       </c>
     </row>
@@ -3239,6 +3239,58 @@
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>12:41:28</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>81</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>12:41:28</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>88</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3264,7 +3316,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:20:00</t>
+          <t>Última actualización: 12:42:09</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3539,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:20:00</t>
+          <t>Última actualización: 12:42:09</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:42:09</t>
+          <t>Última actualización: 12:52:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 108</t>
+          <t>Total filas: 112</t>
         </is>
       </c>
     </row>
@@ -3291,6 +3291,110 @@
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>12:51:55</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>12:51:55</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>30</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>12:51:55</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>41</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>12:51:55</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>96</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3303,7 +3407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3316,14 +3420,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:42:09</t>
+          <t>Última actualización: 12:52:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -3514,6 +3618,32 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12:51:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3526,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3539,14 +3669,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:42:09</t>
+          <t>Última actualización: 12:52:36</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -3867,6 +3997,32 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12:52:16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>95</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:52:36</t>
+          <t>Última actualización: 13:24:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 112</t>
+          <t>Total filas: 122</t>
         </is>
       </c>
     </row>
@@ -3395,6 +3395,266 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>24</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>31</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>39</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>39</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>42</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>64</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>76</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>87</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>99</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3407,7 +3667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3420,14 +3680,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:52:36</t>
+          <t>Última actualización: 13:24:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -3644,6 +3904,32 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>13:24:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3656,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3669,14 +3955,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:52:36</t>
+          <t>Última actualización: 13:24:46</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -4023,6 +4309,32 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>13:24:20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:24:46</t>
+          <t>Última actualización: 13:49:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 122</t>
+          <t>Total filas: 128</t>
         </is>
       </c>
     </row>
@@ -3655,6 +3655,162 @@
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>13:48:44</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>14</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>13:48:44</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>51</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>13:48:44</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>60</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>13:48:44</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>74</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>13:48:44</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>85</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>13:48:44</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>86</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3680,7 +3836,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:24:46</t>
+          <t>Última actualización: 13:49:25</t>
         </is>
       </c>
     </row>
@@ -3942,7 +4098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3955,14 +4111,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:24:46</t>
+          <t>Última actualización: 13:49:25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -4335,6 +4491,32 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>13:49:25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>93</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:49:25</t>
+          <t>Última actualización: 14:18:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 128</t>
+          <t>Total filas: 130</t>
         </is>
       </c>
     </row>
@@ -3811,6 +3811,58 @@
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>14:17:32</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>59</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>14:17:32</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>61</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3836,7 +3888,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:49:25</t>
+          <t>Última actualización: 14:18:13</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4111,14 +4163,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:49:25</t>
+          <t>Última actualización: 14:18:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -4517,6 +4569,32 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14:17:53</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:18:13</t>
+          <t>Última actualización: 14:42:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 130</t>
+          <t>Total filas: 138</t>
         </is>
       </c>
     </row>
@@ -3863,6 +3863,214 @@
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>72</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>72</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>72</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>85</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>92</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>93</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>14:41:26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>96</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3888,7 +4096,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:18:13</t>
+          <t>Última actualización: 14:42:12</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4371,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:18:13</t>
+          <t>Última actualización: 14:42:12</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:42:12</t>
+          <t>Última actualización: 14:52:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 138</t>
+          <t>Total filas: 142</t>
         </is>
       </c>
     </row>
@@ -4071,6 +4071,110 @@
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>14:51:47</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>26</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>14:51:47</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>59</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>14:51:47</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>74</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>14:51:47</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>89</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4096,7 +4200,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:42:12</t>
+          <t>Última actualización: 14:52:27</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4371,14 +4475,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:42:12</t>
+          <t>Última actualización: 14:52:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 17</t>
         </is>
       </c>
     </row>
@@ -4803,6 +4907,58 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14:52:07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>74</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14:52:27</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>98</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:52:27</t>
+          <t>Última actualización: 15:29:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 142</t>
+          <t>Total filas: 151</t>
         </is>
       </c>
     </row>
@@ -4175,6 +4175,240 @@
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>9</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>29</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>38</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>47</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>50</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>63</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>86</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>89</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>15:28:31</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>99</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4200,7 +4434,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:52:27</t>
+          <t>Última actualización: 15:29:12</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4475,14 +4709,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 14:52:27</t>
+          <t>Última actualización: 15:29:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 17</t>
+          <t>Total filas: 18</t>
         </is>
       </c>
     </row>
@@ -4959,6 +5193,32 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15:28:52</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>34</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:29:12</t>
+          <t>Última actualización: 15:53:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 151</t>
+          <t>Total filas: 156</t>
         </is>
       </c>
     </row>
@@ -4409,6 +4409,136 @@
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>15:52:42</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>29</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>15:52:42</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>38</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>15:52:42</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>62</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>15:52:42</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>76</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>15:52:42</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>89</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4434,7 +4564,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:29:12</t>
+          <t>Última actualización: 15:53:23</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4839,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:29:12</t>
+          <t>Última actualización: 15:53:23</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F161"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:53:23</t>
+          <t>Última actualización: 16:16:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 156</t>
+          <t>Total filas: 162</t>
         </is>
       </c>
     </row>
@@ -4539,6 +4539,162 @@
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>40</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>48</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>76</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>79</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>91</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>96</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4551,7 +4707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4564,14 +4720,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:53:23</t>
+          <t>Última actualización: 16:16:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -4814,6 +4970,32 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>16:15:44</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>91</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4826,7 +5008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4839,14 +5021,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 15:53:23</t>
+          <t>Última actualización: 16:16:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 18</t>
+          <t>Total filas: 19</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5531,32 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16:16:04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>51</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:16:24</t>
+          <t>Última actualización: 16:30:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 162</t>
+          <t>Total filas: 168</t>
         </is>
       </c>
     </row>
@@ -4695,6 +4695,162 @@
         </is>
       </c>
       <c r="F167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16:29:54</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>24</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>16:29:54</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>37</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>16:29:54</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>79</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>16:29:54</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>83</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>16:29:54</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>89</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>16:29:54</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>96</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4720,7 +4876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:16:24</t>
+          <t>Última actualización: 16:30:40</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5021,14 +5177,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:16:24</t>
+          <t>Última actualización: 16:30:40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 19</t>
+          <t>Total filas: 20</t>
         </is>
       </c>
     </row>
@@ -5557,6 +5713,32 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16:30:14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>36</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:30:40</t>
+          <t>Última actualización: 16:43:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 168</t>
+          <t>Total filas: 179</t>
         </is>
       </c>
     </row>
@@ -4851,6 +4851,292 @@
         </is>
       </c>
       <c r="F173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>14</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>40</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>53</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>55</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>65</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>67</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>72</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>77</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>84</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>89</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>18:18</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>96</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4863,7 +5149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4876,14 +5162,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:30:40</t>
+          <t>Última actualización: 16:43:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -5152,6 +5438,32 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>16:42:22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5177,7 +5489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:30:40</t>
+          <t>Última actualización: 16:43:08</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:43:08</t>
+          <t>Última actualización: 16:53:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 179</t>
+          <t>Total filas: 186</t>
         </is>
       </c>
     </row>
@@ -5137,6 +5137,188 @@
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>54</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>61</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>78</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>85</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>90</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>93</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>98</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5149,7 +5331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5162,14 +5344,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:43:08</t>
+          <t>Última actualización: 16:53:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -5464,6 +5646,32 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16:52:25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5489,7 +5697,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:43:08</t>
+          <t>Última actualización: 16:53:11</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:53:11</t>
+          <t>Última actualización: 17:23:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 186</t>
+          <t>Total filas: 194</t>
         </is>
       </c>
     </row>
@@ -5319,6 +5319,214 @@
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>30</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>64</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>76</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>80</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>84</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>91</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>17:22:19</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>96</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5344,7 +5552,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:53:11</t>
+          <t>Última actualización: 17:23:04</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5697,14 +5905,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 16:53:11</t>
+          <t>Última actualización: 17:23:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 20</t>
+          <t>Total filas: 21</t>
         </is>
       </c>
     </row>
@@ -6259,6 +6467,32 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>17:22:39</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>74</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:23:04</t>
+          <t>Última actualización: 17:44:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 194</t>
+          <t>Total filas: 203</t>
         </is>
       </c>
     </row>
@@ -5527,6 +5527,240 @@
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>3</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>49</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>76</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>80</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>87</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>91</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>19:16</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>92</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>93</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>98</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5539,7 +5773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5552,14 +5786,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:23:04</t>
+          <t>Última actualización: 17:44:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -5880,6 +6114,58 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17:44:08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5905,7 +6191,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:23:04</t>
+          <t>Última actualización: 17:44:54</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:F217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:44:54</t>
+          <t>Última actualización: 17:56:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 203</t>
+          <t>Total filas: 212</t>
         </is>
       </c>
     </row>
@@ -5761,6 +5761,240 @@
         </is>
       </c>
       <c r="F208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>42</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>46</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>50</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>18:52</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>57</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>62</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>75</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>82</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>86</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>93</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5773,7 +6007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,14 +6020,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:44:54</t>
+          <t>Última actualización: 17:56:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -6166,6 +6400,32 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>17:55:23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>93</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6178,7 +6438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6191,14 +6451,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:44:54</t>
+          <t>Última actualización: 17:56:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 21</t>
+          <t>Total filas: 22</t>
         </is>
       </c>
     </row>
@@ -6779,6 +7039,32 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>17:56:04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>89</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F217"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:56:04</t>
+          <t>Última actualización: 18:19:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 212</t>
+          <t>Total filas: 217</t>
         </is>
       </c>
     </row>
@@ -5995,6 +5995,136 @@
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>18:18:28</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>26</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>18:18:28</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>19:23</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>65</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>18:18:28</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>81</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>18:18:28</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>81_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>94</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>18:18:28</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>95</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6020,7 +6150,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:56:04</t>
+          <t>Última actualización: 18:19:09</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,14 +6581,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 17:56:04</t>
+          <t>Última actualización: 18:19:09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 22</t>
+          <t>Total filas: 23</t>
         </is>
       </c>
     </row>
@@ -7065,6 +7195,32 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>18:19:09</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>65</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:19:09</t>
+          <t>Última actualización: 18:41:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 217</t>
+          <t>Total filas: 221</t>
         </is>
       </c>
     </row>
@@ -6125,6 +6125,110 @@
         </is>
       </c>
       <c r="F222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>18:40:23</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>83</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>18:40:23</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>87</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>18:40:23</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>89</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>18:40:23</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>93</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6137,7 +6241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6150,14 +6254,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:19:09</t>
+          <t>Última actualización: 18:41:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -6556,6 +6660,32 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>18:40:23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>87</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6568,7 +6698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6581,14 +6711,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:19:09</t>
+          <t>Última actualización: 18:41:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 23</t>
+          <t>Total filas: 24</t>
         </is>
       </c>
     </row>
@@ -7221,6 +7351,32 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>18:40:44</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>78</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F226"/>
+  <dimension ref="A1:F232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:41:04</t>
+          <t>Última actualización: 18:51:04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 221</t>
+          <t>Total filas: 227</t>
         </is>
       </c>
     </row>
@@ -6229,6 +6229,162 @@
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>18:50:23</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>34</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>18:50:23</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>40</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>18:50:23</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>19:36</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>46</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>18:50:23</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>50</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>18:50:23</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>19:54</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>64</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>18:50:23</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>92</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6254,7 +6410,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:41:04</t>
+          <t>Última actualización: 18:51:04</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6867,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:41:04</t>
+          <t>Última actualización: 18:51:04</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F232"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:51:04</t>
+          <t>Última actualización: 19:20:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 227</t>
+          <t>Total filas: 234</t>
         </is>
       </c>
     </row>
@@ -6385,6 +6385,188 @@
         </is>
       </c>
       <c r="F232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>34</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>48</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>72</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>72</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>86</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>89</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>98</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6397,7 +6579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6410,14 +6592,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:51:04</t>
+          <t>Última actualización: 19:20:06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 16</t>
         </is>
       </c>
     </row>
@@ -6842,6 +7024,32 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19:19:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:48</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>89</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6867,7 +7075,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:51:04</t>
+          <t>Última actualización: 19:20:06</t>
         </is>
       </c>
     </row>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F239"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:20:06</t>
+          <t>Última actualización: 19:44:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 234</t>
+          <t>Total filas: 243</t>
         </is>
       </c>
     </row>
@@ -6567,6 +6567,240 @@
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>25</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>29</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>47</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>51</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>63</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>64</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>72</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>21:06</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>83</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>87</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6579,7 +6813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6592,14 +6826,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:20:06</t>
+          <t>Última actualización: 19:44:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 16</t>
+          <t>Total filas: 17</t>
         </is>
       </c>
     </row>
@@ -7050,6 +7284,32 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19:43:50</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:47</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>64</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7062,7 +7322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7075,14 +7335,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:20:06</t>
+          <t>Última actualización: 19:44:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 24</t>
+          <t>Total filas: 25</t>
         </is>
       </c>
     </row>
@@ -7741,6 +8001,32 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>19:44:10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:52</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>68</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:44:35</t>
+          <t>Última actualización: 19:55:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 243</t>
+          <t>Total filas: 247</t>
         </is>
       </c>
     </row>
@@ -6801,6 +6801,110 @@
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>19:54:21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>62</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>19:54:21</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>20:56</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>62</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>19:54:21</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>73</v>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>19:54:21</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>95</v>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6826,7 +6930,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:44:35</t>
+          <t>Última actualización: 19:55:07</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7335,14 +7439,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:44:35</t>
+          <t>Última actualización: 19:55:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 25</t>
+          <t>Total filas: 26</t>
         </is>
       </c>
     </row>
@@ -8027,6 +8131,32 @@
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>19:54:42</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>19:57</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:55:07</t>
+          <t>Última actualización: 20:20:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 247</t>
+          <t>Total filas: 253</t>
         </is>
       </c>
     </row>
@@ -6905,6 +6905,162 @@
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>16</v>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>20:57</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>38</v>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>75</v>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>80</v>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>87</v>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20:19:19</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>88</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6930,7 +7086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:55:07</t>
+          <t>Última actualización: 20:20:05</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7439,14 +7595,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 19:55:07</t>
+          <t>Última actualización: 20:20:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 26</t>
+          <t>Total filas: 27</t>
         </is>
       </c>
     </row>
@@ -8157,6 +8313,32 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20:19:40</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>71</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:20:05</t>
+          <t>Última actualización: 20:41:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 253</t>
+          <t>Total filas: 260</t>
         </is>
       </c>
     </row>
@@ -7061,6 +7061,188 @@
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>15</v>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>48</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>21:34</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>54</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>65</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>21:50</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>70</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>84</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20:40:59</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>22:11</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>91</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7086,7 +7268,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:20:05</t>
+          <t>Última actualización: 20:41:45</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7595,14 +7777,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:20:05</t>
+          <t>Última actualización: 20:41:45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 27</t>
+          <t>Total filas: 28</t>
         </is>
       </c>
     </row>
@@ -8339,6 +8521,32 @@
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20:41:19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:41:45</t>
+          <t>Última actualización: 20:52:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 260</t>
+          <t>Total filas: 266</t>
         </is>
       </c>
     </row>
@@ -7243,6 +7243,162 @@
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20:52:08</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>19</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20:52:08</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>43</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20:52:08</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>43</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>20:52:08</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>60</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>20:52:08</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>22:05</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>73</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>20:52:08</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>22:12</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>80</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7268,7 +7424,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:41:45</t>
+          <t>Última actualización: 20:52:49</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7777,14 +7933,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:41:45</t>
+          <t>Última actualización: 20:52:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 28</t>
+          <t>Total filas: 30</t>
         </is>
       </c>
     </row>
@@ -8547,6 +8703,58 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20:52:28</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20:54</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20:52:49</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>22:20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-40 Y 115</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>88</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-01-11.xlsx
+++ b/data/horarios-141-2026-01-11.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F271"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:52:49</t>
+          <t>Última actualización: 22:46:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 266</t>
+          <t>Total filas: 270</t>
         </is>
       </c>
     </row>
@@ -7399,6 +7399,110 @@
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>22:46:08</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>18</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>22:46:08</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>23:20</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>34</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>22:46:08</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>54</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>22:46:08</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>23:59</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>73</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7411,7 +7515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7424,14 +7528,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:52:49</t>
+          <t>Última actualización: 22:46:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 17</t>
+          <t>Total filas: 18</t>
         </is>
       </c>
     </row>
@@ -7908,6 +8012,32 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22:46:08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>54</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7933,7 +8063,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 20:52:49</t>
+          <t>Última actualización: 22:46:59</t>
         </is>
       </c>
     </row>
